--- a/artfynd/A 38246-2026 artfynd.xlsx
+++ b/artfynd/A 38246-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62362047</v>
+        <v>137406125</v>
       </c>
       <c r="B2" t="n">
-        <v>106156</v>
+        <v>58032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Örberga 9450/5050, Nrk</t>
+          <t>Kalkugnsgärdet, Ödeskärr, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501361</v>
+        <v>501190</v>
       </c>
       <c r="R2" t="n">
-        <v>6537202</v>
+        <v>6537033</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1981-05-17</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1981-05-17</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +780,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62362047</t>
+          <t>https://artportalen.se/Sighting/137406125</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>77632476</v>
+        <v>137407116</v>
       </c>
       <c r="B3" t="n">
-        <v>106156</v>
+        <v>58032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,46 +808,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Örberga 9458/5019, Nrk</t>
+          <t>Kalkugnsgärdet, Ödeskärr, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501330</v>
+        <v>501248</v>
       </c>
       <c r="R3" t="n">
-        <v>6537210</v>
+        <v>6537036</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,12 +867,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-05-05</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-05-05</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,27 +897,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/77632476</t>
+          <t>https://artportalen.se/Sighting/137407116</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>77632497</v>
+        <v>137407502</v>
       </c>
       <c r="B4" t="n">
-        <v>106156</v>
+        <v>58032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,46 +925,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ödeskärr 9468/4973, Nrk</t>
+          <t>Kalkugnsgärdet, Örberga, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501283</v>
+        <v>501332</v>
       </c>
       <c r="R4" t="n">
-        <v>6537219</v>
+        <v>6537031</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,12 +984,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-05-05</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-05-05</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,27 +1014,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/77632497</t>
+          <t>https://artportalen.se/Sighting/137407502</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>58220548</v>
+        <v>137407445</v>
       </c>
       <c r="B5" t="n">
-        <v>104628</v>
+        <v>58191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>103023</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,16 +1064,17 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Luckebo 9550/5050, Nrk</t>
+          <t>Kalkugnsgärdet, Örberga, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501359</v>
+        <v>501327</v>
       </c>
       <c r="R5" t="n">
-        <v>6537302</v>
+        <v>6537044</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1073,12 +1101,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2010-06-04</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2010-06-04</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,27 +1127,687 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Gles lövskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137407445</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137407553</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58696</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103046</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gråsiska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Acanthis flammea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kalkugnsgärdet, Örberga, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>501329</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6537030</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137407553</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>62362047</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Örberga 9450/5050, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>501361</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6537202</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1981-05-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1981-05-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62362047</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>77632476</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Örberga 9458/5019, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>501330</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6537210</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-05-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-05-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77632476</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>77632497</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ödeskärr 9468/4973, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>501283</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6537219</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-05-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-05-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77632497</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>58220548</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Luckebo 9550/5050, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>501359</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6537302</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2010-06-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2010-06-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gles lövskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/58220548</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137407055</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101634</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kalkugnsgärdet, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>501242</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6537008</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137407055</t>
         </is>
       </c>
     </row>
@@ -1119,6 +1817,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38246-2026 artfynd.xlsx
+++ b/artfynd/A 38246-2026 artfynd.xlsx
@@ -1703,7 +1703,7 @@
         <v>137407055</v>
       </c>
       <c r="B11" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 38246-2026 artfynd.xlsx
+++ b/artfynd/A 38246-2026 artfynd.xlsx
@@ -1703,7 +1703,7 @@
         <v>137407055</v>
       </c>
       <c r="B11" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 38246-2026 artfynd.xlsx
+++ b/artfynd/A 38246-2026 artfynd.xlsx
@@ -1703,7 +1703,7 @@
         <v>137407055</v>
       </c>
       <c r="B11" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 38246-2026 artfynd.xlsx
+++ b/artfynd/A 38246-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137406125</v>
       </c>
       <c r="B2" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137407116</v>
       </c>
       <c r="B3" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>137407502</v>
       </c>
       <c r="B4" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>137407445</v>
       </c>
       <c r="B5" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137407553</v>
       </c>
       <c r="B6" t="n">
-        <v>58696</v>
+        <v>58699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137407055</v>
       </c>
       <c r="B11" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
